--- a/pcb/Project Outputs for chronos-pcb/BOM/Bill of Materials-chronos-pcb.xlsx
+++ b/pcb/Project Outputs for chronos-pcb/BOM/Bill of Materials-chronos-pcb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\chronos\pcb\Project Outputs for chronos-pcb\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F6E1AD5-50DC-455E-9CEE-E4C30510A9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{82A2CFB2-267B-4FCE-8A9D-48A14B09DB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9E0DFB89-FA97-4AFB-A92A-FA08D26BF3E2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{686A9452-E5D3-4C30-AEA9-3975A1721525}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-chronos-pcb" sheetId="1" r:id="rId1"/>
@@ -1118,7 +1118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD04744-8130-4C6C-B8EA-8499AACD0408}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A8B1F9-49C4-4926-A342-76C8E0D2563F}">
   <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
